--- a/Team-Data/2014-15/3-13-2014-15.xlsx
+++ b/Team-Data/2014-15/3-13-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>0.785</v>
+        <v>0.781</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
@@ -688,19 +755,19 @@
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
         <v>8.6</v>
@@ -709,13 +776,13 @@
         <v>32.2</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
         <v>25.6</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W2" t="n">
         <v>8.800000000000001</v>
@@ -730,19 +797,19 @@
         <v>17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC2" t="n">
         <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -751,10 +818,10 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -766,16 +833,16 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN2" t="n">
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>4</v>
@@ -799,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
@@ -811,7 +878,7 @@
         <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.438</v>
+        <v>0.429</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -870,7 +937,7 @@
         <v>8.1</v>
       </c>
       <c r="M3" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N3" t="n">
         <v>0.331</v>
@@ -882,55 +949,55 @@
         <v>19.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R3" t="n">
         <v>11.3</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF3" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -975,22 +1042,22 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
         <v>26</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1115,13 +1182,13 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>21</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1142,7 +1209,7 @@
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>0.453</v>
+        <v>0.444</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J5" t="n">
         <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,28 +1304,28 @@
         <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.743</v>
+        <v>0.74</v>
       </c>
       <c r="R5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
         <v>12</v>
@@ -1267,7 +1334,7 @@
         <v>5.9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.3</v>
@@ -1279,25 +1346,25 @@
         <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1306,7 +1373,7 @@
         <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1333,10 +1400,10 @@
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,19 +1415,19 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -1389,55 +1456,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.597</v>
+        <v>0.606</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
         <v>83.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.357</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
         <v>34</v>
       </c>
       <c r="T6" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U6" t="n">
         <v>21.6</v>
@@ -1455,34 +1522,34 @@
         <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD6" t="n">
         <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ6" t="n">
         <v>16</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1521,16 +1588,16 @@
         <v>16</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
@@ -1539,7 +1606,7 @@
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -1655,16 +1722,16 @@
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
@@ -1685,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
@@ -1694,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1703,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1715,10 +1782,10 @@
         <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -1756,34 +1823,34 @@
         <v>66</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.636</v>
+        <v>0.621</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O8" t="n">
         <v>16.5</v>
@@ -1792,25 +1859,25 @@
         <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>4.7</v>
@@ -1822,37 +1889,37 @@
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.7</v>
+        <v>104.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
         <v>9</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1861,25 +1928,25 @@
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT8" t="n">
         <v>23</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>21</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1900,10 +1967,10 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -1935,55 +2002,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.379</v>
+        <v>0.369</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J9" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L9" t="n">
         <v>7.7</v>
       </c>
       <c r="M9" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.318</v>
+        <v>0.316</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="R9" t="n">
         <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U9" t="n">
         <v>21.7</v>
@@ -1992,31 +2059,31 @@
         <v>14.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
         <v>22.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
         <v>23</v>
@@ -2034,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
@@ -2046,10 +2113,10 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP9" t="n">
         <v>9</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2058,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>15</v>
@@ -2073,7 +2140,7 @@
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="L10" t="n">
         <v>8.300000000000001</v>
@@ -2147,31 +2214,31 @@
         <v>24.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O10" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.709</v>
+        <v>0.708</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S10" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T10" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W10" t="n">
         <v>7.7</v>
@@ -2183,40 +2250,40 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB10" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>10</v>
@@ -2231,7 +2298,7 @@
         <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2255,13 +2322,13 @@
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA10" t="n">
         <v>22</v>
@@ -2270,7 +2337,7 @@
         <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
         <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.797</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,7 +2384,7 @@
         <v>41.4</v>
       </c>
       <c r="J11" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.477</v>
@@ -2326,7 +2393,7 @@
         <v>10.6</v>
       </c>
       <c r="M11" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="N11" t="n">
         <v>0.391</v>
@@ -2344,40 +2411,40 @@
         <v>10.3</v>
       </c>
       <c r="S11" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
         <v>27</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W11" t="n">
         <v>9.4</v>
       </c>
       <c r="X11" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y11" t="n">
         <v>3.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.5</v>
+        <v>109.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2425,13 +2492,13 @@
         <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.656</v>
+        <v>0.662</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="M12" t="n">
         <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>22</v>
@@ -2547,22 +2614,22 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
         <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2571,13 +2638,13 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2595,7 +2662,7 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,7 +2671,7 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
         <v>14</v>
@@ -2616,16 +2683,16 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>0.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2771,19 +2838,19 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2795,7 +2862,7 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
@@ -2816,7 +2883,7 @@
         <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="n">
         <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.636</v>
+        <v>0.646</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2872,58 +2939,58 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O14" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.715</v>
+        <v>0.717</v>
       </c>
       <c r="R14" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T14" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U14" t="n">
         <v>24.4</v>
       </c>
       <c r="V14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W14" t="n">
         <v>7.8</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.1</v>
+        <v>106.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2956,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2968,10 +3035,10 @@
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27</v>
+        <v>0.266</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3144,10 +3211,10 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3156,7 +3223,7 @@
         <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3165,13 +3232,13 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,10 +3369,10 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>8</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
@@ -3344,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0.446</v>
+        <v>0.453</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
@@ -3421,7 +3488,7 @@
         <v>20.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
         <v>18.1</v>
@@ -3433,22 +3500,22 @@
         <v>0.743</v>
       </c>
       <c r="R17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T17" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="U17" t="n">
         <v>20.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
@@ -3457,7 +3524,7 @@
         <v>4.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
         <v>21</v>
@@ -3466,22 +3533,22 @@
         <v>94.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3490,22 +3557,22 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3523,7 +3590,7 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
         <v>10</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3669,10 +3736,10 @@
         <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3684,13 +3751,13 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3708,16 +3775,16 @@
         <v>29</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J19" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K19" t="n">
         <v>0.434</v>
@@ -3782,19 +3849,19 @@
         <v>4.8</v>
       </c>
       <c r="M19" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.765</v>
+        <v>0.763</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
@@ -3830,28 +3897,28 @@
         <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.9</v>
+        <v>-7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF19" t="n">
         <v>28</v>
       </c>
       <c r="AG19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.547</v>
+        <v>0.554</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3967,37 +4034,37 @@
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O20" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,40 +4073,40 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
@@ -4048,22 +4115,22 @@
         <v>6</v>
       </c>
       <c r="AO20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT20" t="n">
         <v>15</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4218,10 +4285,10 @@
         <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
@@ -4266,7 +4333,7 @@
         <v>27</v>
       </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -4301,58 +4368,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K22" t="n">
         <v>0.445</v>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
         <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="O22" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P22" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.765</v>
+        <v>0.762</v>
       </c>
       <c r="R22" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S22" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="T22" t="n">
         <v>47.5</v>
       </c>
       <c r="U22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V22" t="n">
         <v>14.8</v>
@@ -4373,22 +4440,22 @@
         <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.5</v>
+        <v>102.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF22" t="n">
         <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
         <v>12</v>
@@ -4397,10 +4464,10 @@
         <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>6</v>
@@ -4418,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4439,13 +4506,13 @@
         <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -4501,67 +4568,67 @@
         <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.726</v>
+        <v>0.732</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
         <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB23" t="n">
         <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,19 +4646,19 @@
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4600,7 +4667,7 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
@@ -4618,19 +4685,19 @@
         <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA23" t="n">
         <v>30</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -4665,49 +4732,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
         <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>0.231</v>
+        <v>0.219</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="J24" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.409</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
         <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="O24" t="n">
         <v>16.3</v>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.676</v>
+        <v>0.677</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="n">
         <v>31.2</v>
@@ -4716,7 +4783,7 @@
         <v>42.9</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V24" t="n">
         <v>18.3</v>
@@ -4731,28 +4798,28 @@
         <v>5.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA24" t="n">
         <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>91</v>
+        <v>90.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
@@ -4761,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="J25" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="K25" t="n">
         <v>0.456</v>
@@ -4877,16 +4944,16 @@
         <v>26</v>
       </c>
       <c r="N25" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O25" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P25" t="n">
         <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R25" t="n">
         <v>11</v>
@@ -4895,16 +4962,16 @@
         <v>32</v>
       </c>
       <c r="T25" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U25" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V25" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X25" t="n">
         <v>4.8</v>
@@ -4913,19 +4980,19 @@
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA25" t="n">
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.6</v>
+        <v>104.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4940,31 +5007,31 @@
         <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
       </c>
       <c r="AM25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
@@ -4976,28 +5043,28 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
       </c>
       <c r="AW25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J26" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K26" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L26" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P26" t="n">
         <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.802</v>
+        <v>0.801</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5077,40 +5144,40 @@
         <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
@@ -5122,13 +5189,13 @@
         <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
@@ -5167,19 +5234,19 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H27" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I27" t="n">
         <v>36.3</v>
       </c>
       <c r="J27" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L27" t="n">
         <v>5.3</v>
@@ -5241,16 +5308,16 @@
         <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="P27" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R27" t="n">
         <v>11.1</v>
@@ -5259,13 +5326,13 @@
         <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V27" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5274,34 +5341,34 @@
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z27" t="n">
         <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC27" t="n">
         <v>-4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5337,7 +5404,7 @@
         <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5355,13 +5422,13 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.619</v>
+        <v>0.625</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,52 +5478,52 @@
         <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
         <v>24</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
         <v>19.5</v>
@@ -5471,64 +5538,64 @@
         <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J29" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.453</v>
@@ -5602,34 +5669,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O29" t="n">
         <v>19.3</v>
       </c>
       <c r="P29" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T29" t="n">
         <v>41.4</v>
       </c>
       <c r="U29" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
         <v>7.8</v>
@@ -5647,31 +5714,31 @@
         <v>20.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.4</v>
+        <v>104.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK29" t="n">
         <v>14</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
@@ -5704,7 +5771,7 @@
         <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
@@ -5716,16 +5783,16 @@
         <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
         <v>11</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF30" t="n">
         <v>20</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>19</v>
       </c>
       <c r="AG30" t="n">
         <v>20</v>
@@ -5868,13 +5935,13 @@
         <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
@@ -5895,7 +5962,7 @@
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,10 +6096,10 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ31" t="n">
         <v>20</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6062,10 +6129,10 @@
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
@@ -6083,7 +6150,7 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-13-2014-15</t>
+          <t>2015-03-13</t>
         </is>
       </c>
     </row>
